--- a/forms/trg/Formulir_TRG_dege-rg.xlsx
+++ b/forms/trg/Formulir_TRG_dege-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sri Undai Nurbayani, S.E.,M.Si.</t>
+          <t>Prof. Dr. Nursini, SE., MA</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -933,7 +933,11 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57209198032</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -946,12 +950,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Sultan Suhab, S.E., M.Si.</t>
+          <t>Dr. Sri Undai Nurbayani, S.E.,M.Si.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -966,11 +970,7 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>57209206788</t>
-        </is>
-      </c>
+      <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -983,12 +983,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Agussalim, S.E., M.Si.</t>
+          <t>Dr. Sultan Suhab, S.E., M.Si.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1005,7 +1005,7 @@
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57875521300</t>
+          <t>57209206788</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Harun, MAcc</t>
+          <t>Dr. Agussalim, S.E., M.Si.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>James Cook University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -1038,15 +1038,11 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-4870-5523</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>55361217000</t>
+          <t>57875521300</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1061,17 +1057,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Randi Kurniawan, S.E., M.Sc</t>
+          <t>Dr. Harun, MAcc</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>James Cook University</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
@@ -1079,9 +1075,17 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-4870-5523</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>55361217000</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1094,12 +1098,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Rakhmat Nurul Prima Nugraha, SE., M.Sc</t>
+          <t>Randi Kurniawan, S.E., M.Sc</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1127,12 +1131,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Adya Utami Syukri, SE., M.Si.</t>
+          <t>Rakhmat Nurul Prima Nugraha, SE., M.Sc</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1145,11 +1149,7 @@
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-4545-3711</t>
-        </is>
-      </c>
+      <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="11" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Andi Nur Ildha Arfanita, S.E., M.Dev.Econ., M.Si.</t>
+          <t>Dr. Adya Utami Syukri, SE., M.Si.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1182,7 +1182,11 @@
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-4545-3711</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
@@ -1197,12 +1201,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Muh Alif Febri Ramli, S.E.</t>
+          <t>Andi Nur Ildha Arfanita, S.E., M.Dev.Econ., M.Si.</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1230,12 +1234,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Nur Ainun Wirfiana, S.E.</t>
+          <t>Muh Alif Febri Ramli, S.E.</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1243,11 +1247,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>G-NOMICS Team</t>
-        </is>
-      </c>
+      <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1265,10 +1265,26 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Nur Ainun Wirfiana, S.E.</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>G-NOMICS Team</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
@@ -1276,7 +1292,11 @@
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1465,15 +1485,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
